--- a/artfynd/A 63807-2021 artfynd.xlsx
+++ b/artfynd/A 63807-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63807-2021 artfynd.xlsx
+++ b/artfynd/A 63807-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68277444</v>
+        <v>68277439</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>2383</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394982.3492539459</v>
+        <v>394982</v>
       </c>
       <c r="R2" t="n">
-        <v>6633529.685643235</v>
+        <v>6633530</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -751,21 +746,11 @@
           <t>2015-05-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-05-21</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,6 +759,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>På marken i fuktigt läge</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -790,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68277439</v>
+        <v>68277436</v>
       </c>
       <c r="B3" t="n">
-        <v>92683</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,37 +791,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2383</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Avdelning 32- Sundsberg, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394982.3492539459</v>
+        <v>394982</v>
       </c>
       <c r="R3" t="n">
-        <v>6633529.685643235</v>
+        <v>6633530</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -866,21 +850,11 @@
           <t>2015-05-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-05-21</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -892,7 +866,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>På marken i fuktigt läge</t>
+          <t>På stammen av asp, sälg och äldre rönn</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -910,15 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68277436</v>
+        <v>68277446</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,36 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>222395</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Avdelning 32- Sundsberg, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394982.3492539459</v>
+        <v>394982</v>
       </c>
       <c r="R4" t="n">
-        <v>6633529.685643235</v>
+        <v>6633530</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -985,21 +955,11 @@
           <t>2015-05-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-05-21</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,11 +968,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>På stammen av asp, sälg och äldre rönn</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1029,15 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68277446</v>
+        <v>68277444</v>
       </c>
       <c r="B5" t="n">
-        <v>101323</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,16 +995,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1072,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394982.3492539459</v>
+        <v>394982</v>
       </c>
       <c r="R5" t="n">
-        <v>6633529.685643235</v>
+        <v>6633530</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1105,19 +1055,9 @@
           <t>2015-05-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-05-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,6 +1081,103 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>88417837</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Selma spa, VSV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>394915</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6633613</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-09-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-09-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karin Kjellberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karin Kjellberg, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
